--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741DD973-2F00-4BBE-85D5-EF8893300CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D398C5-3B4D-4F9E-BE35-4A082B30EF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="319">
   <si>
     <t>0</t>
   </si>
@@ -435,10 +435,6 @@
   </si>
   <si>
     <t>goldGain</t>
-  </si>
-  <si>
-    <t>foodGain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>radius</t>
@@ -1188,6 +1184,12 @@
   <si>
     <t>4</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foodGain</t>
+  </si>
+  <si>
+    <t>u16</t>
   </si>
 </sst>
 </file>
@@ -1732,53 +1734,53 @@
         <v>110</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G1" s="14"/>
       <c r="H1" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>54</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="W1" s="14" t="s">
         <v>104</v>
@@ -1787,28 +1789,28 @@
         <v>105</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Z1" s="14" t="s">
         <v>102</v>
       </c>
       <c r="AA1" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB1" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AC1" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AF1" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG1" s="9" t="s">
         <v>53</v>
@@ -1882,89 +1884,89 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>109</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>55</v>
       </c>
       <c r="Q3" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="U3" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="R3" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>279</v>
-      </c>
       <c r="V3" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="W3" s="8" t="s">
         <v>111</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>112</v>
+        <v>317</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Z3" s="8" t="s">
         <v>103</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AE3" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG3" s="13" t="s">
         <v>107</v>
@@ -1973,13 +1975,13 @@
         <v>106</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AJ3" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AK3" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AL3" s="8"/>
       <c r="AM3" s="8"/>
@@ -2011,7 +2013,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J4" s="15" t="s">
         <v>8</v>
@@ -2029,7 +2031,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>6</v>
@@ -2047,16 +2049,16 @@
         <v>8</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>6</v>
+        <v>318</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2068,7 +2070,7 @@
         <v>108</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AC4" s="15" t="s">
         <v>8</v>
@@ -2095,7 +2097,7 @@
         <v>5</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.15">
@@ -2116,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -2125,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
@@ -2146,10 +2148,10 @@
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
       <c r="W5" s="4">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="X5" s="4">
-        <v>650</v>
+        <v>5600</v>
       </c>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4">
@@ -2159,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC5" s="4">
         <v>250</v>
@@ -2193,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -2202,16 +2204,16 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
@@ -2223,10 +2225,10 @@
       <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="4">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="X6" s="4">
-        <v>270</v>
+        <v>2800</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4">
@@ -2236,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC6" s="4">
         <v>100</v>
@@ -2256,7 +2258,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -2269,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -2278,16 +2280,16 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
@@ -2299,10 +2301,10 @@
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
       <c r="W7" s="4">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X7" s="4">
-        <v>310</v>
+        <v>2800</v>
       </c>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4">
@@ -2312,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC7" s="4">
         <v>50</v>
@@ -2321,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
@@ -2332,7 +2334,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2345,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -2354,7 +2356,7 @@
         <v>1500</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>1</v>
@@ -2363,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
@@ -2384,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC8" s="4">
         <v>0</v>
@@ -2397,16 +2399,16 @@
       </c>
       <c r="AF8" s="4"/>
       <c r="AG8" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AM8" s="4"/>
     </row>
@@ -2415,7 +2417,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2428,7 +2430,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J9" s="4">
         <v>26</v>
@@ -2437,7 +2439,7 @@
         <v>2000</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>1</v>
@@ -2446,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
@@ -2467,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC9" s="4">
         <v>0</v>
@@ -2476,20 +2478,20 @@
         <v>0</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AF9" s="4"/>
       <c r="AG9" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AM9" s="4"/>
     </row>
@@ -2498,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2511,7 +2513,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J10" s="4">
         <v>27</v>
@@ -2520,7 +2522,7 @@
         <v>2500</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>1</v>
@@ -2529,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6">
@@ -2552,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC10" s="4">
         <v>0</v>
@@ -2565,16 +2567,16 @@
       </c>
       <c r="AF10" s="4"/>
       <c r="AG10" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AM10" s="4"/>
     </row>
@@ -2583,7 +2585,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -2596,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J11" s="4">
         <v>0</v>
@@ -2608,13 +2610,13 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6">
@@ -2637,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC11" s="4">
         <v>0</v>
@@ -2650,16 +2652,16 @@
       </c>
       <c r="AF11" s="4"/>
       <c r="AG11" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM11" s="4"/>
     </row>
@@ -2681,7 +2683,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J12" s="4">
         <v>26</v>
@@ -2693,13 +2695,13 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6">
@@ -2722,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC12" s="4">
         <v>0</v>
@@ -2735,16 +2737,16 @@
       </c>
       <c r="AF12" s="4"/>
       <c r="AG12" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM12" s="4"/>
     </row>
@@ -2753,7 +2755,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D13" s="4">
         <v>2</v>
@@ -2766,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J13" s="4">
         <v>0</v>
@@ -2784,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -2805,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC13" s="4">
         <v>0</v>
@@ -2816,7 +2818,7 @@
       </c>
       <c r="AF13" s="4"/>
       <c r="AG13" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AM13" s="4"/>
     </row>
@@ -2838,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J14" s="4">
         <v>22</v>
@@ -2856,7 +2858,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -2877,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC14" s="4">
         <v>0</v>
@@ -2888,7 +2890,7 @@
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AM14" s="4"/>
     </row>
@@ -2910,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4">
         <v>23</v>
@@ -2925,10 +2927,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
@@ -2951,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC15" s="4">
         <v>0</v>
@@ -2964,7 +2966,7 @@
       </c>
       <c r="AF15" s="4"/>
       <c r="AG15" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AM15" s="4"/>
     </row>
@@ -2986,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J16" s="4">
         <v>0</v>
@@ -3004,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
@@ -3027,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC16" s="4">
         <v>0</v>
@@ -3040,7 +3042,7 @@
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AM16" s="4"/>
     </row>
@@ -3062,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J17" s="4">
         <v>0</v>
@@ -3080,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6">
@@ -3103,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC17" s="4">
         <v>0</v>
@@ -3116,7 +3118,7 @@
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AM17" s="4"/>
     </row>
@@ -3138,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J18" s="4">
         <v>22</v>
@@ -3156,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6">
@@ -3179,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC18" s="4">
         <v>0</v>
@@ -3192,7 +3194,7 @@
       </c>
       <c r="AF18" s="4"/>
       <c r="AG18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AM18" s="4"/>
     </row>
@@ -3201,7 +3203,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -3214,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J19" s="4">
         <v>0</v>
@@ -3232,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -3251,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC19" s="4">
         <v>0</v>
@@ -3282,7 +3284,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J20" s="4">
         <v>0</v>
@@ -3300,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -3319,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC20" s="4">
         <v>0</v>
@@ -3337,7 +3339,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D21" s="4">
         <v>3</v>
@@ -3350,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J21" s="4">
         <v>0</v>
@@ -3368,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
@@ -3389,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC21" s="4">
         <v>0</v>
@@ -3400,7 +3402,7 @@
       </c>
       <c r="AF21" s="4"/>
       <c r="AG21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM21" s="4"/>
     </row>
@@ -3409,7 +3411,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -3422,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J22" s="4">
         <v>31</v>
@@ -3440,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
@@ -3461,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC22" s="4">
         <v>0</v>
@@ -3472,7 +3474,7 @@
       </c>
       <c r="AF22" s="4"/>
       <c r="AG22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM22" s="4"/>
     </row>
@@ -3494,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J23" s="4">
         <v>0</v>
@@ -3512,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
@@ -3533,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC23" s="4">
         <v>0</v>
@@ -3544,7 +3546,7 @@
       </c>
       <c r="AF23" s="4"/>
       <c r="AG23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AM23" s="4"/>
     </row>
@@ -3566,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J24" s="4">
         <v>31</v>
@@ -3584,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
@@ -3605,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC24" s="4">
         <v>0</v>
@@ -3616,7 +3618,7 @@
       </c>
       <c r="AF24" s="4"/>
       <c r="AG24" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AM24" s="4"/>
     </row>
@@ -3638,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J25" s="4">
         <v>0</v>
@@ -3656,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -3677,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC25" s="4">
         <v>0</v>
@@ -3688,7 +3690,7 @@
       </c>
       <c r="AF25" s="4"/>
       <c r="AG25" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AM25" s="4"/>
     </row>
@@ -3710,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J26" s="4">
         <v>32</v>
@@ -3728,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
@@ -3749,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC26" s="4">
         <v>0</v>
@@ -3760,7 +3762,7 @@
       </c>
       <c r="AF26" s="4"/>
       <c r="AG26" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AM26" s="4"/>
     </row>
@@ -3769,7 +3771,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
@@ -3782,7 +3784,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J27" s="4">
         <v>32</v>
@@ -3800,7 +3802,7 @@
         <v>1</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6"/>
@@ -3821,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC27" s="4">
         <v>0</v>
@@ -3832,7 +3834,7 @@
       </c>
       <c r="AF27" s="4"/>
       <c r="AG27" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AM27" s="4"/>
     </row>
@@ -3854,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J28" s="4">
         <v>0</v>
@@ -3872,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
@@ -3891,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC28" s="4">
         <v>0</v>
@@ -3922,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J29" s="4">
         <v>0</v>
@@ -3940,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
@@ -3959,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC29" s="4">
         <v>0</v>
@@ -3990,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J30" s="4">
         <v>0</v>
@@ -4006,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
@@ -4025,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC30" s="4">
         <v>0</v>
@@ -4056,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J31" s="4">
         <v>0</v>
@@ -4074,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P31" s="6"/>
       <c r="Q31" s="6"/>
@@ -4093,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC31" s="4">
         <v>0</v>
@@ -4124,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J32" s="4">
         <v>0</v>
@@ -4140,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
@@ -4159,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC32" s="4">
         <v>0</v>
@@ -4190,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J33" s="4">
         <v>0</v>
@@ -4208,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
@@ -4227,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC33" s="4">
         <v>0</v>
@@ -4258,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J34" s="4">
         <v>0</v>
@@ -4276,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
@@ -4295,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC34" s="4">
         <v>0</v>
@@ -4326,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J35" s="4">
         <v>0</v>
@@ -4344,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
@@ -4365,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="AB35" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC35" s="4">
         <v>100</v>
@@ -4375,7 +4377,7 @@
         <v>85</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG35" s="4"/>
       <c r="AM35" s="4"/>
@@ -4385,7 +4387,7 @@
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D36" s="4">
         <v>4</v>
@@ -4400,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J36" s="4">
         <v>0</v>
@@ -4418,21 +4420,21 @@
         <v>1</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="6">
         <v>1</v>
       </c>
       <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
+      <c r="S36" s="4"/>
       <c r="T36" s="6">
         <v>2</v>
       </c>
       <c r="U36" s="6"/>
       <c r="V36" s="6"/>
       <c r="W36" s="4">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
@@ -4443,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="AB36" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC36" s="4">
         <v>30</v>
@@ -4455,19 +4457,19 @@
         <v>86</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AM36" s="4"/>
     </row>
@@ -4476,7 +4478,7 @@
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -4491,7 +4493,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J37" s="4">
         <v>0</v>
@@ -4509,14 +4511,14 @@
         <v>1</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="6">
         <v>1</v>
       </c>
       <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
+      <c r="S37" s="4"/>
       <c r="T37" s="6">
         <v>1</v>
       </c>
@@ -4524,7 +4526,7 @@
       <c r="V37" s="6"/>
       <c r="W37" s="4"/>
       <c r="X37" s="4">
-        <v>225</v>
+        <v>1000</v>
       </c>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4">
@@ -4534,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC37" s="4">
         <v>30</v>
@@ -4546,19 +4548,19 @@
         <v>87</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AM37" s="4"/>
     </row>
@@ -4567,7 +4569,7 @@
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -4576,13 +4578,13 @@
         <v>34</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H38" s="4">
         <v>1</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J38" s="4">
         <v>0</v>
@@ -4600,22 +4602,22 @@
         <v>0</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4626,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC38" s="4">
         <v>30</v>
@@ -4638,19 +4640,19 @@
         <v>88</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="2:39" x14ac:dyDescent="0.15">
@@ -4658,7 +4660,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
@@ -4667,13 +4669,13 @@
         <v>35</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H39" s="4">
         <v>1</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J39" s="4">
         <v>0</v>
@@ -4691,22 +4693,22 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -4717,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC39" s="4">
         <v>30</v>
@@ -4729,19 +4731,19 @@
         <v>89</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="2:39" x14ac:dyDescent="0.15">
@@ -4749,7 +4751,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
@@ -4758,13 +4760,13 @@
         <v>36</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H40" s="4">
         <v>1</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J40" s="4">
         <v>0</v>
@@ -4782,22 +4784,22 @@
         <v>0</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -4808,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC40" s="4">
         <v>30</v>
@@ -4820,19 +4822,19 @@
         <v>90</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="2:39" x14ac:dyDescent="0.15">
@@ -4840,7 +4842,7 @@
         <v>37</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -4849,13 +4851,13 @@
         <v>37</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H41" s="4">
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J41" s="4">
         <v>0</v>
@@ -4873,22 +4875,22 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -4899,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="AB41" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC41" s="4">
         <v>30</v>
@@ -4911,19 +4913,19 @@
         <v>91</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="2:39" x14ac:dyDescent="0.15">
@@ -4931,7 +4933,7 @@
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D42" s="4">
         <v>4</v>
@@ -4940,13 +4942,13 @@
         <v>38</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H42" s="4">
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J42" s="4">
         <v>0</v>
@@ -4964,22 +4966,22 @@
         <v>0</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -4990,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC42" s="4">
         <v>30</v>
@@ -5002,19 +5004,19 @@
         <v>92</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="2:39" x14ac:dyDescent="0.15">
@@ -5034,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J43" s="4">
         <v>0</v>
@@ -5052,13 +5054,13 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
@@ -5069,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="AB43" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC43" s="4">
         <v>30</v>
@@ -5082,19 +5084,19 @@
       </c>
       <c r="AF43" s="4"/>
       <c r="AG43" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK43" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="2:39" x14ac:dyDescent="0.15">
@@ -5102,7 +5104,7 @@
         <v>40</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" s="4">
         <v>4</v>
@@ -5114,7 +5116,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J44" s="4">
         <v>0</v>
@@ -5132,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
@@ -5149,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC44" s="4">
         <v>30</v>
@@ -5162,19 +5164,19 @@
       </c>
       <c r="AF44" s="4"/>
       <c r="AG44" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK44" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="2:39" x14ac:dyDescent="0.15">
@@ -5194,7 +5196,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J45" s="4">
         <v>0</v>
@@ -5212,16 +5214,16 @@
         <v>0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
@@ -5232,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="AB45" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC45" s="4">
         <v>30</v>
@@ -5241,22 +5243,22 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="2:39" x14ac:dyDescent="0.15">
@@ -5264,7 +5266,7 @@
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5276,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J46" s="4">
         <v>0</v>
@@ -5294,25 +5296,25 @@
         <v>0</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5323,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="AB46" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC46" s="4">
         <v>30</v>
@@ -5332,22 +5334,22 @@
         <v>1</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="2:39" x14ac:dyDescent="0.15">
@@ -5367,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J47" s="4">
         <v>0</v>
@@ -5385,19 +5387,19 @@
         <v>0</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
@@ -5408,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC47" s="4">
         <v>30</v>
@@ -5417,22 +5419,22 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="2:39" x14ac:dyDescent="0.15">
@@ -5452,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J48" s="4">
         <v>0</v>
@@ -5470,16 +5472,16 @@
         <v>0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
@@ -5490,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC48" s="4">
         <v>30</v>
@@ -5502,19 +5504,19 @@
         <v>95</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="2:37" x14ac:dyDescent="0.15">
@@ -5534,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J49" s="4">
         <v>0</v>
@@ -5552,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
@@ -5572,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC49" s="4">
         <v>30</v>
@@ -5584,19 +5586,19 @@
         <v>96</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="2:37" x14ac:dyDescent="0.15">
@@ -5604,7 +5606,7 @@
         <v>46</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D50" s="4">
         <v>4</v>
@@ -5616,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J50" s="4">
         <v>0</v>
@@ -5634,22 +5636,22 @@
         <v>0</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -5660,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC50" s="4">
         <v>30</v>
@@ -5669,22 +5671,22 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="2:37" x14ac:dyDescent="0.15">
@@ -5704,7 +5706,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J51" s="4">
         <v>0</v>
@@ -5722,19 +5724,20 @@
         <v>0</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="S51" s="4"/>
       <c r="T51" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W51" s="4">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="X51" s="4"/>
       <c r="Z51" s="4">
@@ -5744,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="AB51" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC51" s="4">
         <v>30</v>
@@ -5756,19 +5759,19 @@
         <v>97</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="2:37" x14ac:dyDescent="0.15">
@@ -5788,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J52" s="4">
         <v>0</v>
@@ -5806,19 +5809,20 @@
         <v>0</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="S52" s="4"/>
       <c r="T52" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W52" s="4">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="X52" s="4"/>
       <c r="Z52" s="4">
@@ -5828,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC52" s="4">
         <v>30</v>
@@ -5840,19 +5844,19 @@
         <v>98</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="2:37" x14ac:dyDescent="0.15">
@@ -5872,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J53" s="4">
         <v>0</v>
@@ -5890,16 +5894,17 @@
         <v>0</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="S53" s="4"/>
       <c r="T53" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W53" s="4">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="X53" s="4"/>
       <c r="Z53" s="4">
@@ -5909,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="AB53" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC53" s="4">
         <v>0</v>
@@ -5922,16 +5927,16 @@
       </c>
       <c r="AF53" s="4"/>
       <c r="AG53" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="2:37" x14ac:dyDescent="0.15">
@@ -5951,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J54" s="4">
         <v>0</v>
@@ -5969,20 +5974,21 @@
         <v>0</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="S54" s="4"/>
       <c r="T54" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W54" s="4"/>
       <c r="X54" s="4">
-        <v>250</v>
+        <v>1600</v>
       </c>
       <c r="Z54" s="4">
         <v>400</v>
@@ -5991,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AB54" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC54" s="4">
         <v>30</v>
@@ -6003,22 +6009,22 @@
         <v>100</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AK54" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55" spans="2:37" x14ac:dyDescent="0.15">
@@ -6035,13 +6041,13 @@
         <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H55" s="4">
         <v>2</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J55" s="4">
         <v>0</v>
@@ -6059,16 +6065,17 @@
         <v>0</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="S55" s="4"/>
       <c r="T55" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W55" s="4">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="X55" s="4"/>
       <c r="Z55" s="4">
@@ -6078,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC55" s="4">
         <v>20</v>
@@ -6091,16 +6098,16 @@
       </c>
       <c r="AF55" s="4"/>
       <c r="AG55" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="2:37" x14ac:dyDescent="0.15">
@@ -6120,7 +6127,7 @@
         <v>3</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J56" s="4">
         <v>0</v>
@@ -6138,16 +6145,17 @@
         <v>0</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="S56" s="4"/>
       <c r="T56" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W56" s="4">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="X56" s="4"/>
       <c r="Z56" s="4">
@@ -6157,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="AB56" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC56" s="4">
         <v>20</v>
@@ -6170,16 +6178,16 @@
       </c>
       <c r="AF56" s="4"/>
       <c r="AG56" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ56" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="2:37" x14ac:dyDescent="0.15">
@@ -6196,13 +6204,13 @@
         <v>33</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H57" s="4">
         <v>2</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J57" s="4">
         <v>0</v>
@@ -6220,17 +6228,18 @@
         <v>0</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="S57" s="4"/>
       <c r="T57" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W57" s="4"/>
       <c r="X57" s="4">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="Z57" s="4">
         <v>200</v>
@@ -6239,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="AB57" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC57" s="4">
         <v>20</v>
@@ -6252,16 +6261,16 @@
       </c>
       <c r="AF57" s="4"/>
       <c r="AG57" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="2:37" x14ac:dyDescent="0.15">
@@ -6281,7 +6290,7 @@
         <v>3</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J58" s="4">
         <v>0</v>
@@ -6299,17 +6308,18 @@
         <v>0</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>122</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="S58" s="4"/>
       <c r="T58" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W58" s="4"/>
       <c r="X58" s="4">
-        <v>350</v>
+        <v>1600</v>
       </c>
       <c r="Z58" s="4">
         <v>200</v>
@@ -6318,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC58" s="4">
         <v>20</v>
@@ -6331,16 +6341,16 @@
       </c>
       <c r="AF58" s="4"/>
       <c r="AG58" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ58" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="2:37" x14ac:dyDescent="0.15">
@@ -6357,13 +6367,13 @@
         <v>34</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H59" s="4">
         <v>2</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J59" s="4">
         <v>0</v>
@@ -6381,22 +6391,22 @@
         <v>0</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6407,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC59" s="4">
         <v>20</v>
@@ -6420,16 +6430,16 @@
       </c>
       <c r="AF59" s="4"/>
       <c r="AG59" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AH59" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" spans="2:37" x14ac:dyDescent="0.15">
@@ -6449,7 +6459,7 @@
         <v>3</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J60" s="4">
         <v>0</v>
@@ -6467,22 +6477,22 @@
         <v>0</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6493,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC60" s="4">
         <v>20</v>
@@ -6506,16 +6516,16 @@
       </c>
       <c r="AF60" s="4"/>
       <c r="AG60" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AH60" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="2:37" x14ac:dyDescent="0.15">
@@ -6532,13 +6542,13 @@
         <v>35</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H61" s="4">
         <v>2</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J61" s="4">
         <v>0</v>
@@ -6556,22 +6566,22 @@
         <v>0</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -6582,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="AB61" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC61" s="4">
         <v>20</v>
@@ -6595,16 +6605,16 @@
       </c>
       <c r="AF61" s="4"/>
       <c r="AG61" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AH61" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AI61" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ61" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="2:37" x14ac:dyDescent="0.15">
@@ -6624,7 +6634,7 @@
         <v>3</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J62" s="4">
         <v>0</v>
@@ -6642,22 +6652,22 @@
         <v>0</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -6668,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AB62" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC62" s="4">
         <v>20</v>
@@ -6681,16 +6691,16 @@
       </c>
       <c r="AF62" s="4"/>
       <c r="AG62" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AH62" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AI62" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ62" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="2:37" x14ac:dyDescent="0.15">
@@ -6713,7 +6723,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J63" s="4">
         <v>0</v>
@@ -6731,22 +6741,22 @@
         <v>0</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -6758,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="AB63" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC63" s="4">
         <v>20</v>
@@ -6771,16 +6781,16 @@
       </c>
       <c r="AF63" s="4"/>
       <c r="AG63" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AH63" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI63" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="AI63" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="AJ63" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="64" spans="2:37" x14ac:dyDescent="0.15">
@@ -6801,7 +6811,7 @@
         <v>3</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J64" s="4">
         <v>0</v>
@@ -6819,22 +6829,22 @@
         <v>0</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -6846,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="AB64" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC64" s="4">
         <v>20</v>
@@ -6859,16 +6869,16 @@
       </c>
       <c r="AF64" s="4"/>
       <c r="AG64" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AH64" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI64" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="AI64" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="AJ64" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="2:39" x14ac:dyDescent="0.15">
@@ -6876,7 +6886,7 @@
         <v>61</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D65" s="4">
         <v>4</v>
@@ -6885,13 +6895,13 @@
         <v>37</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H65" s="4">
         <v>2</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J65" s="4">
         <v>0</v>
@@ -6909,22 +6919,22 @@
         <v>0</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -6935,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="AB65" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC65" s="4">
         <v>30</v>
@@ -6948,16 +6958,16 @@
       </c>
       <c r="AF65" s="4"/>
       <c r="AG65" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH65" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ65" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="66" spans="2:39" x14ac:dyDescent="0.15">
@@ -6965,7 +6975,7 @@
         <v>62</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D66" s="4">
         <v>4</v>
@@ -6977,7 +6987,7 @@
         <v>3</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J66" s="4">
         <v>0</v>
@@ -6995,22 +7005,22 @@
         <v>0</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7021,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="AB66" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC66" s="4">
         <v>30</v>
@@ -7034,16 +7044,16 @@
       </c>
       <c r="AF66" s="4"/>
       <c r="AG66" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AH66" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI66" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ66" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="2:39" x14ac:dyDescent="0.15">
@@ -7051,7 +7061,7 @@
         <v>63</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D67" s="4">
         <v>4</v>
@@ -7060,13 +7070,13 @@
         <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H67" s="4">
         <v>2</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J67" s="4">
         <v>0</v>
@@ -7084,22 +7094,22 @@
         <v>0</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7110,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="AB67" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC67" s="4">
         <v>30</v>
@@ -7123,16 +7133,16 @@
       </c>
       <c r="AF67" s="4"/>
       <c r="AG67" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH67" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ67" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" spans="2:39" x14ac:dyDescent="0.15">
@@ -7140,7 +7150,7 @@
         <v>64</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D68" s="4">
         <v>4</v>
@@ -7152,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J68" s="4">
         <v>0</v>
@@ -7170,22 +7180,22 @@
         <v>0</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7196,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AC68" s="4">
         <v>30</v>
@@ -7209,16 +7219,16 @@
       </c>
       <c r="AF68" s="4"/>
       <c r="AG68" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH68" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AI68" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AJ68" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="2:39" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D398C5-3B4D-4F9E-BE35-4A082B30EF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C79E5C-F864-4BBE-9005-7153A2888C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="320">
   <si>
     <t>0</t>
   </si>
@@ -560,39 +560,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4845_8_7</t>
-  </si>
-  <si>
-    <t>4845_8_6</t>
-  </si>
-  <si>
-    <t>4845_5_25</t>
-  </si>
-  <si>
-    <t>4845_8_8</t>
-  </si>
-  <si>
-    <t>4845_8_9</t>
-  </si>
-  <si>
-    <t>4845_8_11</t>
-  </si>
-  <si>
-    <t>4845_8_12</t>
-  </si>
-  <si>
-    <t>4845_8_10</t>
-  </si>
-  <si>
-    <t>4845_8_13</t>
-  </si>
-  <si>
-    <t>4845_7_15</t>
-  </si>
-  <si>
-    <t>4845_7_12</t>
-  </si>
-  <si>
     <t>港</t>
   </si>
   <si>
@@ -642,84 +609,6 @@
   <si>
     <t>强化位于周围３区格内己方部队之防御，并减轻其兵粮消费</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4845_7_13</t>
-  </si>
-  <si>
-    <t>4845_7_14</t>
-  </si>
-  <si>
-    <t>4845_7_16</t>
-  </si>
-  <si>
-    <t>4845_7_17</t>
-  </si>
-  <si>
-    <t>4845_7_18</t>
-  </si>
-  <si>
-    <t>4845_7_19</t>
-  </si>
-  <si>
-    <t>4845_7_20</t>
-  </si>
-  <si>
-    <t>4845_7_21</t>
-  </si>
-  <si>
-    <t>4845_7_22</t>
-  </si>
-  <si>
-    <t>4845_7_23</t>
-  </si>
-  <si>
-    <t>4845_7_24</t>
-  </si>
-  <si>
-    <t>4845_8_0</t>
-  </si>
-  <si>
-    <t>4845_8_1</t>
-  </si>
-  <si>
-    <t>4845_8_2</t>
-  </si>
-  <si>
-    <t>4845_8_3</t>
-  </si>
-  <si>
-    <t>4845_8_4</t>
-  </si>
-  <si>
-    <t>4845_8_14</t>
-  </si>
-  <si>
-    <t>4845_5_34</t>
-  </si>
-  <si>
-    <t>4845_5_22</t>
-  </si>
-  <si>
-    <t>4845_5_23</t>
-  </si>
-  <si>
-    <t>4845_5_24</t>
-  </si>
-  <si>
-    <t>4845_5_26</t>
-  </si>
-  <si>
-    <t>4845_5_27</t>
-  </si>
-  <si>
-    <t>4845_5_28</t>
-  </si>
-  <si>
-    <t>4845_5_29</t>
-  </si>
-  <si>
-    <t>4845_5_30</t>
   </si>
   <si>
     <t>limitDesc</t>
@@ -1190,6 +1079,120 @@
   </si>
   <si>
     <t>u16</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_12</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_13</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_14</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_15</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_16</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_17</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_18</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_19</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_20</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_21</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_22</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_23</t>
+  </si>
+  <si>
+    <t>4846-8/4846-8_24</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_0</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_1</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_2</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_3</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_4</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_5</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_6</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_7</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_8</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_9</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_10</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_11</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_12</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_13</t>
+  </si>
+  <si>
+    <t>4846-9/4846-9_14</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_34</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_22</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_23</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_24</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_25</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_26</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_27</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_28</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_29</t>
+  </si>
+  <si>
+    <t>4846-6/4846-6_30</t>
   </si>
 </sst>
 </file>
@@ -1692,36 +1695,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AN120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="19.5" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.08984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.08984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.7265625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="19.453125" style="2" customWidth="1"/>
     <col min="16" max="22" width="17" style="2" customWidth="1"/>
-    <col min="23" max="24" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.25" style="2" customWidth="1"/>
-    <col min="29" max="29" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="71.875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.875" style="2" customWidth="1"/>
-    <col min="36" max="36" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="102.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.26953125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="71.90625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="21.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.90625" style="2" customWidth="1"/>
+    <col min="36" max="36" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="102.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:40" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -1741,10 +1744,10 @@
         <v>142</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>51</v>
@@ -1765,22 +1768,22 @@
         <v>54</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="W1" s="14" t="s">
         <v>104</v>
@@ -1795,22 +1798,22 @@
         <v>102</v>
       </c>
       <c r="AA1" s="14" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="AB1" s="18" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="AC1" s="14" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AF1" s="14" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="AG1" s="9" t="s">
         <v>53</v>
@@ -1829,7 +1832,7 @@
       <c r="AM1" s="9"/>
       <c r="AN1" s="7"/>
     </row>
-    <row r="2" spans="1:40" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:40" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1873,7 +1876,7 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
     </row>
-    <row r="3" spans="1:40" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:40" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1884,7 +1887,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>109</v>
@@ -1897,10 +1900,10 @@
         <v>141</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>113</v>
@@ -1921,28 +1924,28 @@
         <v>55</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="W3" s="8" t="s">
         <v>111</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
       <c r="Y3" s="8" t="s">
         <v>116</v>
@@ -1954,19 +1957,19 @@
         <v>112</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="AE3" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="AG3" s="13" t="s">
         <v>107</v>
@@ -1975,19 +1978,19 @@
         <v>106</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="AJ3" s="13" t="s">
         <v>129</v>
       </c>
       <c r="AK3" s="8" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="AL3" s="8"/>
       <c r="AM3" s="8"/>
       <c r="AN3" s="8"/>
     </row>
-    <row r="4" spans="1:40" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:40" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2013,7 +2016,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="J4" s="15" t="s">
         <v>8</v>
@@ -2049,16 +2052,16 @@
         <v>8</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2070,7 +2073,7 @@
         <v>108</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="AC4" s="15" t="s">
         <v>8</v>
@@ -2097,10 +2100,10 @@
         <v>5</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.15">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2176,7 +2179,7 @@
       <c r="AG5" s="4"/>
       <c r="AM5" s="4"/>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -2253,12 +2256,12 @@
       <c r="AG6" s="4"/>
       <c r="AM6" s="4"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -2323,18 +2326,18 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
       <c r="AM7" s="4"/>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2399,25 +2402,25 @@
       </c>
       <c r="AF8" s="4"/>
       <c r="AG8" s="2" t="s">
-        <v>153</v>
+        <v>282</v>
       </c>
       <c r="AH8" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="AM8" s="4"/>
     </row>
-    <row r="9" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2448,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
@@ -2478,29 +2481,29 @@
         <v>0</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="AF9" s="4"/>
       <c r="AG9" s="2" t="s">
-        <v>168</v>
+        <v>283</v>
       </c>
       <c r="AH9" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="AM9" s="4"/>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2567,25 +2570,25 @@
       </c>
       <c r="AF10" s="4"/>
       <c r="AG10" s="2" t="s">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="AH10" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="AM10" s="4"/>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -2652,20 +2655,20 @@
       </c>
       <c r="AF11" s="4"/>
       <c r="AG11" s="2" t="s">
-        <v>152</v>
+        <v>285</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="AM11" s="4"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2737,25 +2740,25 @@
       </c>
       <c r="AF12" s="4"/>
       <c r="AG12" s="2" t="s">
-        <v>170</v>
+        <v>286</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="AM12" s="4"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D13" s="4">
         <v>2</v>
@@ -2818,11 +2821,11 @@
       </c>
       <c r="AF13" s="4"/>
       <c r="AG13" s="2" t="s">
-        <v>171</v>
+        <v>287</v>
       </c>
       <c r="AM13" s="4"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2890,11 +2893,11 @@
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="2" t="s">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="AM14" s="4"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2966,11 +2969,11 @@
       </c>
       <c r="AF15" s="4"/>
       <c r="AG15" s="2" t="s">
-        <v>173</v>
+        <v>289</v>
       </c>
       <c r="AM15" s="4"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -3042,11 +3045,11 @@
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="2" t="s">
-        <v>174</v>
+        <v>290</v>
       </c>
       <c r="AM16" s="4"/>
     </row>
-    <row r="17" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -3118,11 +3121,11 @@
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="2" t="s">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="AM17" s="4"/>
     </row>
-    <row r="18" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -3194,16 +3197,16 @@
       </c>
       <c r="AF18" s="4"/>
       <c r="AG18" s="2" t="s">
-        <v>176</v>
+        <v>292</v>
       </c>
       <c r="AM18" s="4"/>
     </row>
-    <row r="19" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -3266,7 +3269,7 @@
       <c r="AG19" s="4"/>
       <c r="AM19" s="4"/>
     </row>
-    <row r="20" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -3334,12 +3337,12 @@
       <c r="AG20" s="4"/>
       <c r="AM20" s="4"/>
     </row>
-    <row r="21" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D21" s="4">
         <v>3</v>
@@ -3402,16 +3405,16 @@
       </c>
       <c r="AF21" s="4"/>
       <c r="AG21" s="2" t="s">
-        <v>177</v>
+        <v>293</v>
       </c>
       <c r="AM21" s="4"/>
     </row>
-    <row r="22" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -3474,11 +3477,11 @@
       </c>
       <c r="AF22" s="4"/>
       <c r="AG22" s="2" t="s">
-        <v>178</v>
+        <v>294</v>
       </c>
       <c r="AM22" s="4"/>
     </row>
-    <row r="23" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -3546,11 +3549,11 @@
       </c>
       <c r="AF23" s="4"/>
       <c r="AG23" s="2" t="s">
-        <v>179</v>
+        <v>295</v>
       </c>
       <c r="AM23" s="4"/>
     </row>
-    <row r="24" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -3618,11 +3621,11 @@
       </c>
       <c r="AF24" s="4"/>
       <c r="AG24" s="2" t="s">
-        <v>180</v>
+        <v>296</v>
       </c>
       <c r="AM24" s="4"/>
     </row>
-    <row r="25" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3690,11 +3693,11 @@
       </c>
       <c r="AF25" s="4"/>
       <c r="AG25" s="2" t="s">
-        <v>181</v>
+        <v>297</v>
       </c>
       <c r="AM25" s="4"/>
     </row>
-    <row r="26" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3762,16 +3765,16 @@
       </c>
       <c r="AF26" s="4"/>
       <c r="AG26" s="2" t="s">
-        <v>182</v>
+        <v>298</v>
       </c>
       <c r="AM26" s="4"/>
     </row>
-    <row r="27" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
@@ -3834,11 +3837,11 @@
       </c>
       <c r="AF27" s="4"/>
       <c r="AG27" s="2" t="s">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="AM27" s="4"/>
     </row>
-    <row r="28" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -3906,7 +3909,7 @@
       <c r="AG28" s="4"/>
       <c r="AM28" s="4"/>
     </row>
-    <row r="29" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -3974,7 +3977,7 @@
       <c r="AG29" s="4"/>
       <c r="AM29" s="4"/>
     </row>
-    <row r="30" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -4040,7 +4043,7 @@
       <c r="AG30" s="4"/>
       <c r="AM30" s="4"/>
     </row>
-    <row r="31" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -4108,7 +4111,7 @@
       <c r="AG31" s="4"/>
       <c r="AM31" s="4"/>
     </row>
-    <row r="32" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -4174,7 +4177,7 @@
       <c r="AG32" s="4"/>
       <c r="AM32" s="4"/>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -4242,7 +4245,7 @@
       <c r="AG33" s="4"/>
       <c r="AM33" s="4"/>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -4310,7 +4313,7 @@
       <c r="AG34" s="4"/>
       <c r="AM34" s="4"/>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -4377,17 +4380,19 @@
         <v>85</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG35" s="4"/>
+        <v>159</v>
+      </c>
+      <c r="AG35" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="AM35" s="4"/>
     </row>
-    <row r="36" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="D36" s="4">
         <v>4</v>
@@ -4457,28 +4462,28 @@
         <v>86</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="AG36" s="2" t="s">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="AJ36" s="2" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="AM36" s="4"/>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -4548,28 +4553,28 @@
         <v>87</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>143</v>
+        <v>302</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="AM37" s="4"/>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -4578,7 +4583,7 @@
         <v>34</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="H38" s="4">
         <v>1</v>
@@ -4602,22 +4607,22 @@
         <v>0</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4640,27 +4645,27 @@
         <v>88</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>146</v>
+        <v>303</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="39" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B39" s="4">
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
@@ -4669,7 +4674,7 @@
         <v>35</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="H39" s="4">
         <v>1</v>
@@ -4693,22 +4698,22 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q39" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -4731,27 +4736,27 @@
         <v>89</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="40" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B40" s="4">
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
@@ -4760,7 +4765,7 @@
         <v>36</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="H40" s="4">
         <v>1</v>
@@ -4784,22 +4789,22 @@
         <v>0</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q40" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -4822,27 +4827,27 @@
         <v>90</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
         <v>37</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -4851,7 +4856,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="H41" s="4">
         <v>1</v>
@@ -4875,22 +4880,22 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -4913,27 +4918,27 @@
         <v>91</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>148</v>
+        <v>306</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B42" s="4">
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="D42" s="4">
         <v>4</v>
@@ -4942,7 +4947,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="H42" s="4">
         <v>1</v>
@@ -4966,22 +4971,22 @@
         <v>0</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5004,22 +5009,22 @@
         <v>92</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="43" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -5054,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q43" s="2" t="s">
         <v>121</v>
@@ -5084,27 +5089,27 @@
       </c>
       <c r="AF43" s="4"/>
       <c r="AG43" s="2" t="s">
-        <v>151</v>
+        <v>308</v>
       </c>
       <c r="AH43" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI43" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ43" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK43" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="AI43" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AJ43" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AK43" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B44" s="4">
         <v>40</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D44" s="4">
         <v>4</v>
@@ -5134,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>121</v>
@@ -5164,22 +5169,22 @@
       </c>
       <c r="AF44" s="4"/>
       <c r="AG44" s="2" t="s">
-        <v>184</v>
+        <v>309</v>
       </c>
       <c r="AH44" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI44" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ44" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK44" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="AI44" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AJ44" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AK44" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -5214,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>121</v>
@@ -5243,30 +5248,30 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="46" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B46" s="4">
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5296,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P46" s="2" t="s">
         <v>121</v>
@@ -5311,10 +5316,10 @@
         <v>138</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5334,25 +5339,25 @@
         <v>1</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>291</v>
+        <v>254</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>186</v>
+        <v>311</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -5387,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>121</v>
@@ -5399,7 +5404,7 @@
         <v>138</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
@@ -5419,25 +5424,25 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>187</v>
+        <v>312</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -5472,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>121</v>
@@ -5504,22 +5509,22 @@
         <v>95</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>188</v>
+        <v>313</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="49" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="49" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -5554,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>121</v>
@@ -5586,27 +5591,27 @@
         <v>96</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="AG49" s="2" t="s">
-        <v>145</v>
+        <v>314</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="50" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B50" s="4">
         <v>46</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D50" s="4">
         <v>4</v>
@@ -5636,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>121</v>
@@ -5648,10 +5653,10 @@
         <v>138</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>316</v>
+        <v>279</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -5671,25 +5676,25 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="AG50" s="2" t="s">
-        <v>189</v>
+        <v>315</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="51" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -5724,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P51" s="2" t="s">
         <v>121</v>
@@ -5759,22 +5764,22 @@
         <v>97</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="AG51" s="2" t="s">
-        <v>190</v>
+        <v>316</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="52" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -5809,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>121</v>
@@ -5844,22 +5849,22 @@
         <v>98</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="AG52" s="2" t="s">
-        <v>191</v>
+        <v>317</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="53" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="53" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -5894,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>121</v>
@@ -5927,19 +5932,19 @@
       </c>
       <c r="AF53" s="4"/>
       <c r="AG53" s="2" t="s">
-        <v>192</v>
+        <v>318</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="54" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -5974,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>121</v>
@@ -6009,25 +6014,25 @@
         <v>100</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AK54" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="55" spans="2:37" x14ac:dyDescent="0.15">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="55" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -6041,7 +6046,7 @@
         <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="H55" s="4">
         <v>2</v>
@@ -6065,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q55" s="2" t="s">
         <v>121</v>
@@ -6098,19 +6103,19 @@
       </c>
       <c r="AF55" s="4"/>
       <c r="AG55" s="2" t="s">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="56" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="56" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -6145,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>121</v>
@@ -6178,19 +6183,19 @@
       </c>
       <c r="AF56" s="4"/>
       <c r="AG56" s="2" t="s">
-        <v>144</v>
+        <v>301</v>
       </c>
       <c r="AH56" s="2" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ56" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="57" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="57" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -6204,7 +6209,7 @@
         <v>33</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="H57" s="4">
         <v>2</v>
@@ -6228,7 +6233,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>121</v>
@@ -6261,19 +6266,19 @@
       </c>
       <c r="AF57" s="4"/>
       <c r="AG57" s="2" t="s">
-        <v>143</v>
+        <v>302</v>
       </c>
       <c r="AH57" s="2" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="58" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -6308,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q58" s="2" t="s">
         <v>121</v>
@@ -6341,19 +6346,19 @@
       </c>
       <c r="AF58" s="4"/>
       <c r="AG58" s="2" t="s">
-        <v>143</v>
+        <v>302</v>
       </c>
       <c r="AH58" s="2" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ58" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="59" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="59" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -6367,7 +6372,7 @@
         <v>34</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="H59" s="4">
         <v>2</v>
@@ -6391,22 +6396,22 @@
         <v>0</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q59" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6430,19 +6435,19 @@
       </c>
       <c r="AF59" s="4"/>
       <c r="AG59" s="2" t="s">
-        <v>146</v>
+        <v>303</v>
       </c>
       <c r="AH59" s="2" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -6477,22 +6482,22 @@
         <v>0</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q60" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6516,19 +6521,19 @@
       </c>
       <c r="AF60" s="4"/>
       <c r="AG60" s="2" t="s">
-        <v>146</v>
+        <v>303</v>
       </c>
       <c r="AH60" s="2" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="61" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -6542,7 +6547,7 @@
         <v>35</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="H61" s="4">
         <v>2</v>
@@ -6566,22 +6571,22 @@
         <v>0</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q61" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -6605,19 +6610,19 @@
       </c>
       <c r="AF61" s="4"/>
       <c r="AG61" s="2" t="s">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c r="AH61" s="2" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="AI61" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ61" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="62" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -6652,22 +6657,22 @@
         <v>0</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -6691,19 +6696,19 @@
       </c>
       <c r="AF62" s="4"/>
       <c r="AG62" s="2" t="s">
-        <v>147</v>
+        <v>304</v>
       </c>
       <c r="AH62" s="2" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="AI62" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ62" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -6741,22 +6746,22 @@
         <v>0</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -6781,19 +6786,19 @@
       </c>
       <c r="AF63" s="4"/>
       <c r="AG63" s="2" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="AH63" s="2" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="AI63" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ63" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="64" spans="2:37" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -6829,22 +6834,22 @@
         <v>0</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q64" s="2" t="s">
         <v>138</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -6869,24 +6874,24 @@
       </c>
       <c r="AF64" s="4"/>
       <c r="AG64" s="2" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="AH64" s="2" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="AI64" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ64" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
         <v>61</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="D65" s="4">
         <v>4</v>
@@ -6895,7 +6900,7 @@
         <v>37</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="H65" s="4">
         <v>2</v>
@@ -6919,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q65" s="2" t="s">
         <v>138</v>
@@ -6928,13 +6933,13 @@
         <v>134</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -6958,24 +6963,24 @@
       </c>
       <c r="AF65" s="4"/>
       <c r="AG65" s="2" t="s">
-        <v>148</v>
+        <v>306</v>
       </c>
       <c r="AH65" s="2" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ65" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="66" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B66" s="4">
         <v>62</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="D66" s="4">
         <v>4</v>
@@ -7005,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>138</v>
@@ -7014,13 +7019,13 @@
         <v>126</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7044,24 +7049,24 @@
       </c>
       <c r="AF66" s="4"/>
       <c r="AG66" s="2" t="s">
-        <v>148</v>
+        <v>306</v>
       </c>
       <c r="AH66" s="2" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="AI66" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ66" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="67" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
         <v>63</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="D67" s="4">
         <v>4</v>
@@ -7070,7 +7075,7 @@
         <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="H67" s="4">
         <v>2</v>
@@ -7094,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q67" s="2" t="s">
         <v>138</v>
@@ -7103,13 +7108,13 @@
         <v>134</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7133,24 +7138,24 @@
       </c>
       <c r="AF67" s="4"/>
       <c r="AG67" s="2" t="s">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="AH67" s="2" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ67" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B68" s="4">
         <v>64</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="D68" s="4">
         <v>4</v>
@@ -7180,7 +7185,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>138</v>
@@ -7189,13 +7194,13 @@
         <v>126</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7219,19 +7224,19 @@
       </c>
       <c r="AF68" s="4"/>
       <c r="AG68" s="2" t="s">
-        <v>149</v>
+        <v>307</v>
       </c>
       <c r="AH68" s="2" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="AI68" s="2" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AJ68" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="69" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -7247,7 +7252,7 @@
       <c r="AE69" s="4"/>
       <c r="AF69" s="4"/>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -7272,7 +7277,7 @@
       <c r="AF70" s="4"/>
       <c r="AM70" s="4"/>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -7294,7 +7299,7 @@
       <c r="AF71" s="4"/>
       <c r="AM71" s="4"/>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -7316,7 +7321,7 @@
       <c r="AF72" s="4"/>
       <c r="AM72" s="4"/>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -7338,7 +7343,7 @@
       <c r="AF73" s="4"/>
       <c r="AM73" s="4"/>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -7360,7 +7365,7 @@
       <c r="AF74" s="4"/>
       <c r="AM74" s="4"/>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -7382,7 +7387,7 @@
       <c r="AF75" s="4"/>
       <c r="AM75" s="4"/>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7404,7 +7409,7 @@
       <c r="AF76" s="4"/>
       <c r="AM76" s="4"/>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -7426,7 +7431,7 @@
       <c r="AF77" s="4"/>
       <c r="AM77" s="4"/>
     </row>
-    <row r="78" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -7448,7 +7453,7 @@
       <c r="AF78" s="4"/>
       <c r="AM78" s="4"/>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -7470,7 +7475,7 @@
       <c r="AF79" s="4"/>
       <c r="AM79" s="4"/>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -7492,7 +7497,7 @@
       <c r="AF80" s="4"/>
       <c r="AM80" s="4"/>
     </row>
-    <row r="81" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -7514,7 +7519,7 @@
       <c r="AF81" s="4"/>
       <c r="AM81" s="4"/>
     </row>
-    <row r="82" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -7536,7 +7541,7 @@
       <c r="AF82" s="4"/>
       <c r="AM82" s="4"/>
     </row>
-    <row r="83" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -7558,7 +7563,7 @@
       <c r="AF83" s="4"/>
       <c r="AM83" s="4"/>
     </row>
-    <row r="84" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -7580,7 +7585,7 @@
       <c r="AF84" s="4"/>
       <c r="AM84" s="4"/>
     </row>
-    <row r="85" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -7602,7 +7607,7 @@
       <c r="AF85" s="4"/>
       <c r="AM85" s="4"/>
     </row>
-    <row r="86" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -7624,7 +7629,7 @@
       <c r="AF86" s="4"/>
       <c r="AM86" s="4"/>
     </row>
-    <row r="87" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -7646,7 +7651,7 @@
       <c r="AF87" s="4"/>
       <c r="AM87" s="4"/>
     </row>
-    <row r="88" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -7668,7 +7673,7 @@
       <c r="AF88" s="4"/>
       <c r="AM88" s="4"/>
     </row>
-    <row r="89" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -7690,7 +7695,7 @@
       <c r="AF89" s="4"/>
       <c r="AM89" s="4"/>
     </row>
-    <row r="90" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -7712,7 +7717,7 @@
       <c r="AF90" s="4"/>
       <c r="AM90" s="4"/>
     </row>
-    <row r="91" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -7734,7 +7739,7 @@
       <c r="AF91" s="4"/>
       <c r="AM91" s="4"/>
     </row>
-    <row r="92" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -7756,7 +7761,7 @@
       <c r="AF92" s="4"/>
       <c r="AM92" s="4"/>
     </row>
-    <row r="93" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -7769,7 +7774,7 @@
       <c r="AF93" s="4"/>
       <c r="AM93" s="4"/>
     </row>
-    <row r="94" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:39" x14ac:dyDescent="0.25">
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="P94" s="6"/>
@@ -7788,7 +7793,7 @@
       <c r="AF94" s="4"/>
       <c r="AM94" s="4"/>
     </row>
-    <row r="95" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:39" x14ac:dyDescent="0.25">
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="P95" s="6"/>
@@ -7807,7 +7812,7 @@
       <c r="AF95" s="4"/>
       <c r="AM95" s="4"/>
     </row>
-    <row r="96" spans="2:39" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:39" x14ac:dyDescent="0.25">
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="P96" s="6"/>
@@ -7826,7 +7831,7 @@
       <c r="AF96" s="4"/>
       <c r="AM96" s="4"/>
     </row>
-    <row r="97" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="97" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="P97" s="6"/>
@@ -7845,7 +7850,7 @@
       <c r="AF97" s="4"/>
       <c r="AM97" s="4"/>
     </row>
-    <row r="98" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="98" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="P98" s="6"/>
@@ -7864,7 +7869,7 @@
       <c r="AF98" s="4"/>
       <c r="AM98" s="4"/>
     </row>
-    <row r="99" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="99" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="P99" s="6"/>
@@ -7883,7 +7888,7 @@
       <c r="AF99" s="4"/>
       <c r="AM99" s="4"/>
     </row>
-    <row r="100" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="100" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="P100" s="6"/>
@@ -7902,7 +7907,7 @@
       <c r="AF100" s="4"/>
       <c r="AM100" s="4"/>
     </row>
-    <row r="101" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="101" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="P101" s="6"/>
@@ -7921,7 +7926,7 @@
       <c r="AF101" s="4"/>
       <c r="AM101" s="4"/>
     </row>
-    <row r="102" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="102" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="P102" s="6"/>
@@ -7940,7 +7945,7 @@
       <c r="AF102" s="4"/>
       <c r="AM102" s="4"/>
     </row>
-    <row r="103" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="103" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="W103" s="4"/>
@@ -7951,7 +7956,7 @@
       <c r="AE103" s="4"/>
       <c r="AF103" s="4"/>
     </row>
-    <row r="104" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="104" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="W104" s="4"/>
@@ -7962,7 +7967,7 @@
       <c r="AE104" s="4"/>
       <c r="AF104" s="4"/>
     </row>
-    <row r="105" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="105" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="W105" s="4"/>
@@ -7973,7 +7978,7 @@
       <c r="AE105" s="4"/>
       <c r="AF105" s="4"/>
     </row>
-    <row r="106" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="106" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="W106" s="4"/>
@@ -7984,7 +7989,7 @@
       <c r="AE106" s="4"/>
       <c r="AF106" s="4"/>
     </row>
-    <row r="107" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="107" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="W107" s="4"/>
@@ -7995,7 +8000,7 @@
       <c r="AE107" s="4"/>
       <c r="AF107" s="4"/>
     </row>
-    <row r="108" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="108" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="W108" s="4"/>
@@ -8006,7 +8011,7 @@
       <c r="AE108" s="4"/>
       <c r="AF108" s="4"/>
     </row>
-    <row r="109" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="109" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="W109" s="4"/>
@@ -8017,7 +8022,7 @@
       <c r="AE109" s="4"/>
       <c r="AF109" s="4"/>
     </row>
-    <row r="110" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="110" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="W110" s="4"/>
@@ -8028,7 +8033,7 @@
       <c r="AE110" s="4"/>
       <c r="AF110" s="4"/>
     </row>
-    <row r="111" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="111" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="W111" s="4"/>
@@ -8039,7 +8044,7 @@
       <c r="AE111" s="4"/>
       <c r="AF111" s="4"/>
     </row>
-    <row r="112" spans="5:39" x14ac:dyDescent="0.15">
+    <row r="112" spans="5:39" x14ac:dyDescent="0.25">
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="W112" s="4"/>
@@ -8050,7 +8055,7 @@
       <c r="AE112" s="4"/>
       <c r="AF112" s="4"/>
     </row>
-    <row r="113" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="113" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="W113" s="4"/>
@@ -8061,7 +8066,7 @@
       <c r="AE113" s="4"/>
       <c r="AF113" s="4"/>
     </row>
-    <row r="114" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="114" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="W114" s="4"/>
@@ -8072,7 +8077,7 @@
       <c r="AE114" s="4"/>
       <c r="AF114" s="4"/>
     </row>
-    <row r="115" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="115" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="W115" s="4"/>
@@ -8083,7 +8088,7 @@
       <c r="AE115" s="4"/>
       <c r="AF115" s="4"/>
     </row>
-    <row r="116" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="116" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="W116" s="4"/>
@@ -8094,7 +8099,7 @@
       <c r="AE116" s="4"/>
       <c r="AF116" s="4"/>
     </row>
-    <row r="117" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="117" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="W117" s="4"/>
@@ -8105,7 +8110,7 @@
       <c r="AE117" s="4"/>
       <c r="AF117" s="4"/>
     </row>
-    <row r="118" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="118" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="W118" s="4"/>
@@ -8116,7 +8121,7 @@
       <c r="AE118" s="4"/>
       <c r="AF118" s="4"/>
     </row>
-    <row r="119" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="119" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="W119" s="4"/>
@@ -8127,7 +8132,7 @@
       <c r="AE119" s="4"/>
       <c r="AF119" s="4"/>
     </row>
-    <row r="120" spans="5:32" x14ac:dyDescent="0.15">
+    <row r="120" spans="5:32" x14ac:dyDescent="0.25">
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="W120" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C79E5C-F864-4BBE-9005-7153A2888C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DF0A3E-E823-4D9F-8CFB-91C29FB389B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="320">
   <si>
     <t>0</t>
   </si>
@@ -1695,32 +1695,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AN120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="16.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.6328125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.08984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.7265625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="19.453125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="19.44140625" style="2" customWidth="1"/>
     <col min="16" max="22" width="17" style="2" customWidth="1"/>
-    <col min="23" max="24" width="10.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.26953125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="71.90625" style="2" customWidth="1"/>
-    <col min="33" max="33" width="21.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="37.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.90625" style="2" customWidth="1"/>
-    <col min="36" max="36" width="37.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="102.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.21875" style="2" customWidth="1"/>
+    <col min="29" max="29" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="71.88671875" style="2" customWidth="1"/>
+    <col min="33" max="33" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="37.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.88671875" style="2" customWidth="1"/>
+    <col min="36" max="36" width="37.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="102.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -5061,6 +5061,9 @@
       <c r="O43" s="2" t="s">
         <v>184</v>
       </c>
+      <c r="P43" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="Q43" s="2" t="s">
         <v>121</v>
       </c>
@@ -5087,7 +5090,9 @@
       <c r="AE43" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AF43" s="4"/>
+      <c r="AF43" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="AG43" s="2" t="s">
         <v>308</v>
       </c>
@@ -5140,6 +5145,9 @@
       </c>
       <c r="O44" s="2" t="s">
         <v>184</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>121</v>
@@ -5167,7 +5175,9 @@
       <c r="AE44" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="AF44" s="4"/>
+      <c r="AF44" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="AG44" s="2" t="s">
         <v>309</v>
       </c>
